--- a/artfynd/A 40564-2023 artfynd.xlsx
+++ b/artfynd/A 40564-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40564-2023 artfynd.xlsx
+++ b/artfynd/A 40564-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1386,6 +1386,127 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122396270</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98175</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stenkulla, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>557011</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6373886</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vena</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>I barrblandskog med stora tallar ,40 dbh, och yngre granar</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Marcus Lewin</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Marcus Lewin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40564-2023 artfynd.xlsx
+++ b/artfynd/A 40564-2023 artfynd.xlsx
@@ -1391,7 +1391,7 @@
         <v>122396270</v>
       </c>
       <c r="B8" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 40564-2023 artfynd.xlsx
+++ b/artfynd/A 40564-2023 artfynd.xlsx
@@ -1391,7 +1391,7 @@
         <v>122396270</v>
       </c>
       <c r="B8" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 40564-2023 artfynd.xlsx
+++ b/artfynd/A 40564-2023 artfynd.xlsx
@@ -1391,7 +1391,7 @@
         <v>122396270</v>
       </c>
       <c r="B8" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 40564-2023 artfynd.xlsx
+++ b/artfynd/A 40564-2023 artfynd.xlsx
@@ -1391,7 +1391,7 @@
         <v>122396270</v>
       </c>
       <c r="B8" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1405,11 +1405,6 @@
       </c>
       <c r="E8" t="n">
         <v>220787</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>

--- a/artfynd/A 40564-2023 artfynd.xlsx
+++ b/artfynd/A 40564-2023 artfynd.xlsx
@@ -1391,7 +1391,7 @@
         <v>122396270</v>
       </c>
       <c r="B8" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1405,6 +1405,11 @@
       </c>
       <c r="E8" t="n">
         <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>

--- a/artfynd/A 40564-2023 artfynd.xlsx
+++ b/artfynd/A 40564-2023 artfynd.xlsx
@@ -1391,7 +1391,7 @@
         <v>122396270</v>
       </c>
       <c r="B8" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 40564-2023 artfynd.xlsx
+++ b/artfynd/A 40564-2023 artfynd.xlsx
@@ -1391,7 +1391,7 @@
         <v>122396270</v>
       </c>
       <c r="B8" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 40564-2023 artfynd.xlsx
+++ b/artfynd/A 40564-2023 artfynd.xlsx
@@ -1391,7 +1391,7 @@
         <v>122396270</v>
       </c>
       <c r="B8" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 40564-2023 artfynd.xlsx
+++ b/artfynd/A 40564-2023 artfynd.xlsx
@@ -1391,7 +1391,7 @@
         <v>122396270</v>
       </c>
       <c r="B8" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
